--- a/data/trans_bre/P19C06-Estudios-trans_bre.xlsx
+++ b/data/trans_bre/P19C06-Estudios-trans_bre.xlsx
@@ -660,42 +660,42 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-1,88; 0,3</t>
+          <t>-1,86; 0,29</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-0,3; 1,53</t>
+          <t>-0,26; 1,51</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-0,75; 1,9</t>
+          <t>-0,74; 1,95</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-3,66; 1,21</t>
+          <t>-3,97; 1,16</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-77,92; 47,24</t>
+          <t>-77,41; 44,18</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-41,88; 626,21</t>
+          <t>-40,16; 535,15</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-50,91; 430,71</t>
+          <t>-50,76; 463,48</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-82,56; 183,58</t>
+          <t>-81,45; 201,22</t>
         </is>
       </c>
     </row>
@@ -760,42 +760,42 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-0,56; 1,01</t>
+          <t>-0,55; 1,07</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-0,32; 1,3</t>
+          <t>-0,4; 1,23</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-1,02; 0,56</t>
+          <t>-1,02; 0,58</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-0,39; 0,63</t>
+          <t>-0,41; 0,59</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-42,64; 186,37</t>
+          <t>-46,26; 183,27</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-26,14; 179,64</t>
+          <t>-30,07; 171,96</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-54,57; 71,05</t>
+          <t>-55,74; 65,16</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-42,64; 155,53</t>
+          <t>-42,07; 157,16</t>
         </is>
       </c>
     </row>
@@ -860,42 +860,42 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-0,64; 2,46</t>
+          <t>-0,75; 2,55</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-1,37; 1,9</t>
+          <t>-1,36; 1,88</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-0,38; 2,27</t>
+          <t>-0,49; 2,44</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-0,14; 1,76</t>
+          <t>-0,27; 1,67</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-59,28; 872,04</t>
+          <t>-59,16; 650,95</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-80,1; 464,87</t>
+          <t>-76,11; 384,76</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-55,49; 861,7</t>
+          <t>-54,61; 855,45</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-38,93; 672,06</t>
+          <t>-38,04; 633,29</t>
         </is>
       </c>
     </row>
@@ -960,42 +960,42 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-0,65; 0,55</t>
+          <t>-0,59; 0,52</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-0,07; 1,09</t>
+          <t>-0,04; 1,08</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-0,53; 0,72</t>
+          <t>-0,45; 0,81</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-0,26; 0,72</t>
+          <t>-0,35; 0,7</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-45,7; 69,27</t>
+          <t>-40,74; 67,3</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-7,65; 151,97</t>
+          <t>-4,9; 160,83</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-35,55; 82,91</t>
+          <t>-31,08; 92,7</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-24,97; 130,02</t>
+          <t>-32,26; 116,81</t>
         </is>
       </c>
     </row>

--- a/data/trans_bre/P19C06-Estudios-trans_bre.xlsx
+++ b/data/trans_bre/P19C06-Estudios-trans_bre.xlsx
@@ -627,7 +627,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>-0,24</t>
+          <t>0,12</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -647,7 +647,7 @@
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>-13,31%</t>
+          <t>8,96%</t>
         </is>
       </c>
     </row>
@@ -660,42 +660,42 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-1,86; 0,29</t>
+          <t>-1,8; 0,38</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-0,26; 1,51</t>
+          <t>-0,42; 1,43</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-0,74; 1,95</t>
+          <t>-0,89; 1,93</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-3,97; 1,16</t>
+          <t>-1,77; 1,16</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-77,41; 44,18</t>
+          <t>-76,67; 62,62</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-40,16; 535,15</t>
+          <t>-43,68; 469,54</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-50,76; 463,48</t>
+          <t>-59,29; 441,26</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-81,45; 201,22</t>
+          <t>-71,91; 192,7</t>
         </is>
       </c>
     </row>
@@ -727,7 +727,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>0,12</t>
+          <t>0,18</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -747,7 +747,7 @@
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>17,65%</t>
+          <t>26,53%</t>
         </is>
       </c>
     </row>
@@ -760,42 +760,42 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-0,55; 1,07</t>
+          <t>-0,53; 1,04</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-0,4; 1,23</t>
+          <t>-0,35; 1,33</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-1,02; 0,58</t>
+          <t>-1,03; 0,57</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-0,41; 0,59</t>
+          <t>-0,31; 0,7</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-46,26; 183,27</t>
+          <t>-42,06; 191,34</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-30,07; 171,96</t>
+          <t>-26,73; 181,39</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-55,74; 65,16</t>
+          <t>-56,64; 64,58</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-42,07; 157,16</t>
+          <t>-34,43; 147,93</t>
         </is>
       </c>
     </row>
@@ -827,7 +827,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>0,75</t>
+          <t>0,79</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -847,7 +847,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>111,24%</t>
+          <t>124,89%</t>
         </is>
       </c>
     </row>
@@ -860,42 +860,42 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-0,75; 2,55</t>
+          <t>-0,86; 2,47</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-1,36; 1,88</t>
+          <t>-1,31; 1,97</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-0,49; 2,44</t>
+          <t>-0,4; 2,44</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-0,27; 1,67</t>
+          <t>-0,09; 1,76</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-59,16; 650,95</t>
+          <t>-69,91; 592,17</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-76,11; 384,76</t>
+          <t>-71,26; 552,9</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-54,61; 855,45</t>
+          <t>-48,44; 827,37</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-38,04; 633,29</t>
+          <t>-26,25; 729,64</t>
         </is>
       </c>
     </row>
@@ -927,7 +927,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>0,23</t>
+          <t>0,33</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -947,7 +947,7 @@
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>27,2%</t>
+          <t>42,28%</t>
         </is>
       </c>
     </row>
@@ -960,42 +960,42 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-0,59; 0,52</t>
+          <t>-0,48; 0,59</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-0,04; 1,08</t>
+          <t>-0,16; 1,1</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-0,45; 0,81</t>
+          <t>-0,48; 0,74</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-0,35; 0,7</t>
+          <t>-0,13; 0,76</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-40,74; 67,3</t>
+          <t>-34,54; 77,61</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-4,9; 160,83</t>
+          <t>-13,06; 156,87</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-31,08; 92,7</t>
+          <t>-31,88; 88,79</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-32,26; 116,81</t>
+          <t>-16,22; 130,93</t>
         </is>
       </c>
     </row>
